--- a/aq_files/0947.xlsx
+++ b/aq_files/0947.xlsx
@@ -2,12 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python Variables Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,12 +13,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color theme="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -31,28 +37,28 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -125,114 +131,56 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -244,322 +192,820 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="30.5" customWidth="1" style="3" min="1" max="1"/>
+    <col width="21.38" customWidth="1" style="3" min="2" max="26"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Create a variable to store your name and print it.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>What is the first step in ML workflow?</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Model training</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Data collection</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Assign two variables with numbers and print their sum.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>What comes after data collection?</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Data cleaning</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Create variables of type int, float, and string, and print their types.</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Which step prepares data for modeling?</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Data preparation</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Swap values of two variables without using a third variable.</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Which step builds the model?</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Assign multiple variables in one line and print them.</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>What is model evaluation?</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Training model</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Measuring performance</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Cleaning data</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Storing data</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Take user input and store it in a variable, then print its type.</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Which step comes after evaluation?</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Convert a string variable to an integer and perform arithmetic.</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>What is deployment?</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Storing model</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Using model in production</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Cleaning data</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Create a constant variable and try modifying it. Observe behavior.</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Which step improves model performance?</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Data storage</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Hyperparameter tuning</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Use global and local variables in a function and print both.</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Which technique splits data?</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Normalization</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Train-test split</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Encoding</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Aggregation</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Assign a list to a variable and modify one element.</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Which algorithm is used for regression?</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>K-Means</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Linear Regression</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>DBSCAN</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>PCA</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Demonstrate variable unpacking with a tuple.</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Which algorithm is used for classification?</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>K-Means</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>PCA</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>DBSCAN</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Create a variable inside a loop and access it outside.</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Which algorithm is used for clustering?</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Decision Tree</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>K-Means</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Linear Regression</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Demonstrate mutable vs immutable variable behavior.</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Which is a tree-based algorithm?</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Decision Tree</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>K-Means</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PCA</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Naive Bayes</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Use variables to store a dictionary and update values dynamically.</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Which is an ensemble method?</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Linear Regression</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>K-Means</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>PCA</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Create a function that modifies a variable passed as argument.</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Which is a boosting algorithm?</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>K-Means</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>PCA</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Use *args to pass multiple values into a function.</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Which is used in deep learning?</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Neural Networks</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>K-Means</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PCA</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Naive Bayes</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Use **kwargs to store dynamic key-value pairs.</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Which step handles feature creation?</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Feature engineering</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Demonstrate variable shadowing inside nested functions.</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Which metric measures error?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Loss function</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Use variables with lambda functions.</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Which method validates model?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Cross-validation</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Encoding</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Create a class and use instance variables and class variables.</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Which outputs predictions?</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
